--- a/Semiconductor/PXLW.xlsx
+++ b/Semiconductor/PXLW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/Models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433FA1FA-650F-5944-B6E0-B55C54EBEF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B40F83B-4995-A949-BC1B-3B11A2E84911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22280" yWindow="8920" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{E6F64D46-DD00-774A-9F7E-6D373F60E178}"/>
+    <workbookView xWindow="20880" yWindow="4260" windowWidth="29120" windowHeight="20900" xr2:uid="{E6F64D46-DD00-774A-9F7E-6D373F60E178}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
   <si>
     <t>S</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Vecima Networks -- Canadian broadband</t>
+  </si>
+  <si>
+    <t>Q325</t>
   </si>
 </sst>
 </file>
@@ -684,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2">
-        <v>0.89</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="3" spans="2:8">
@@ -695,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>58.938408000000003</v>
+        <v>6.2935449999999999</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -707,7 +710,7 @@
       </c>
       <c r="G4" s="1">
         <f>+G3*G2</f>
-        <v>52.455183120000001</v>
+        <v>36.69136735</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -715,11 +718,11 @@
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>28.83</v>
+        <v>14.611000000000001</v>
       </c>
       <c r="H5" s="1" t="str">
         <f>+H3</f>
-        <v>Q324</v>
+        <v>Q325</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -730,11 +733,11 @@
         <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1.4039999999999999</v>
       </c>
       <c r="H6" s="1" t="str">
         <f>+H5</f>
-        <v>Q324</v>
+        <v>Q325</v>
       </c>
     </row>
     <row r="7" spans="2:8">
@@ -746,7 +749,7 @@
       </c>
       <c r="G7" s="1">
         <f>+G4-G5+G6</f>
-        <v>23.625183120000003</v>
+        <v>23.484367349999999</v>
       </c>
     </row>
     <row r="8" spans="2:8">
